--- a/services/integrator/internal/document/testdata/stok-nilai-q2-2026.golden.xlsx
+++ b/services/integrator/internal/document/testdata/stok-nilai-q2-2026.golden.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">PT Stok Uji</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t xml:space="preserve">Gula Aren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Manis</t>
   </si>
   <si>
     <t xml:space="preserve">B001</t>
@@ -431,25 +437,22 @@
         <v>17</v>
       </c>
       <c r="D10" s="7">
-        <v>9.666</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="8">
-        <v>840461.99</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7">
         <v>0</v>
       </c>
       <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="8">
         <v>1</v>
-      </c>
-      <c r="I10" s="8">
-        <v>86950.34</v>
-      </c>
-      <c r="J10" s="7">
-        <v>8.666</v>
-      </c>
-      <c r="K10" s="8">
-        <v>753511.65</v>
       </c>
     </row>
     <row r="11">
@@ -463,22 +466,25 @@
         <v>17</v>
       </c>
       <c r="D11" s="7">
-        <v>2.9</v>
+        <v>9.666</v>
       </c>
       <c r="E11" s="8">
-        <v>304500</v>
+        <v>840461.99</v>
       </c>
       <c r="F11" s="7">
         <v>0</v>
       </c>
       <c r="H11" s="7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I11" s="8">
+        <v>86950.34</v>
       </c>
       <c r="J11" s="7">
-        <v>2.9</v>
+        <v>8.666</v>
       </c>
       <c r="K11" s="8">
-        <v>304500</v>
+        <v>753511.65</v>
       </c>
     </row>
     <row r="12">
@@ -492,7 +498,10 @@
         <v>17</v>
       </c>
       <c r="D12" s="7">
-        <v>1</v>
+        <v>2.9</v>
+      </c>
+      <c r="E12" s="8">
+        <v>304500</v>
       </c>
       <c r="F12" s="7">
         <v>0</v>
@@ -501,7 +510,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="7">
-        <v>1</v>
+        <v>2.9</v>
+      </c>
+      <c r="K12" s="8">
+        <v>304500</v>
       </c>
     </row>
     <row r="13">
@@ -512,10 +524,10 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D13" s="7">
-        <v>5.551115123125783e-17</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7">
         <v>0</v>
@@ -524,24 +536,21 @@
         <v>0</v>
       </c>
       <c r="J13" s="7">
-        <v>5.551115123125783e-17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
       <c r="D14" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-87500</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="F14" s="7">
         <v>0</v>
@@ -550,27 +559,24 @@
         <v>0</v>
       </c>
       <c r="J14" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="K14" s="8">
-        <v>-87500</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>35</v>
       </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
       <c r="D15" s="7">
-        <v>0.2</v>
+        <v>-3.5</v>
       </c>
       <c r="E15" s="8">
-        <v>200</v>
+        <v>-87500</v>
       </c>
       <c r="F15" s="7">
         <v>0</v>
@@ -579,10 +585,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="7">
-        <v>0.2</v>
+        <v>-3.5</v>
       </c>
       <c r="K15" s="8">
-        <v>200</v>
+        <v>-87500</v>
       </c>
     </row>
     <row r="16">
@@ -593,13 +599,13 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7">
-        <v>4.6499999999999995</v>
+        <v>0.2</v>
       </c>
       <c r="E16" s="8">
-        <v>211296.7</v>
+        <v>200</v>
       </c>
       <c r="F16" s="7">
         <v>0</v>
@@ -608,10 +614,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="7">
-        <v>4.6499999999999995</v>
+        <v>0.2</v>
       </c>
       <c r="K16" s="8">
-        <v>211296.7</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
@@ -622,13 +628,13 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D17" s="7">
-        <v>3</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="E17" s="8">
-        <v>3</v>
+        <v>211296.7</v>
       </c>
       <c r="F17" s="7">
         <v>0</v>
@@ -637,46 +643,75 @@
         <v>0</v>
       </c>
       <c r="J17" s="7">
-        <v>3</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="K17" s="8">
-        <v>3</v>
+        <v>211296.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
         <v>41</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
       <c r="D18" s="7">
+        <v>3</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.03</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7">
+        <v>3</v>
+      </c>
+      <c r="K18" s="8">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7">
         <v>1</v>
       </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
+      <c r="F19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" s="10">
-        <v>9946936.34</v>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" t="s">
-        <v>44</v>
+      <c r="B20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="10">
+        <v>9946937.37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
